--- a/docs/d/73/inyear.xlsx
+++ b/docs/d/73/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -4147,13 +4147,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>0</v>

--- a/docs/d/73/inyear.xlsx
+++ b/docs/d/73/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,11 @@
       <c r="AB4" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC4" s="4" t="inlineStr"/>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -2257,7 +2261,11 @@
       <c r="AB15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2669,7 +2677,11 @@
       <c r="AB19" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC19" s="4" t="inlineStr"/>
+      <c r="AC19" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -5436,7 +5448,11 @@
       <c r="AB46" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC46" s="4" t="inlineStr"/>
+      <c r="AC46" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -6664,7 +6680,11 @@
       <c r="AB58" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC58" s="4" t="inlineStr"/>
+      <c r="AC58" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -7674,7 +7694,11 @@
       <c r="AB68" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC68" s="4" t="inlineStr"/>
+      <c r="AC68" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -7775,7 +7799,11 @@
       <c r="AB69" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC69" s="4" t="inlineStr"/>
+      <c r="AC69" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -8078,7 +8106,11 @@
       <c r="AB72" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC72" s="4" t="inlineStr"/>
+      <c r="AC72" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -8179,7 +8211,11 @@
       <c r="AB73" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC73" s="4" t="inlineStr"/>
+      <c r="AC73" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -8587,7 +8623,11 @@
       <c r="AB77" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC77" s="4" t="inlineStr"/>
+      <c r="AC77" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -9201,7 +9241,11 @@
       <c r="AB83" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC83" s="4" t="inlineStr"/>
+      <c r="AC83" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -10849,7 +10893,11 @@
       <c r="AB99" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC99" s="4" t="inlineStr"/>
+      <c r="AC99" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -12089,7 +12137,11 @@
       <c r="AB111" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC111" s="4" t="inlineStr"/>
+      <c r="AC111" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -12392,7 +12444,11 @@
       <c r="AB114" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC114" s="4" t="inlineStr"/>
+      <c r="AC114" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">

--- a/docs/d/73/inyear.xlsx
+++ b/docs/d/73/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 31 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 28 clubs short</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1533,8 +1533,8 @@
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="9" t="n">
-        <v>0</v>
+      <c r="Z8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1844,8 +1844,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
@@ -3064,7 +3064,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" s="9" t="n">
         <v>0</v>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4215,8 +4215,8 @@
       <c r="Y34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z34" s="9" t="n">
-        <v>0</v>
+      <c r="Z34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA34" s="10" t="n">
         <v>1</v>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5929,10 +5929,10 @@
         <v>2</v>
       </c>
       <c r="R51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="S51" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T51" s="9" t="n">
         <v>0</v>
@@ -8585,7 +8585,7 @@
         </is>
       </c>
       <c r="P77" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q77" s="9" t="n">
         <v>0</v>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9100,8 +9100,8 @@
       <c r="P82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" s="9" t="n">
-        <v>1</v>
+      <c r="Q82" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R82" s="9" t="n">
         <v>0</v>
@@ -10091,7 +10091,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10105,13 +10105,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
@@ -10149,8 +10149,8 @@
       <c r="U92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V92" s="9" t="n">
-        <v>3</v>
+      <c r="V92" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
@@ -12878,7 +12878,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -12911,7 +12911,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -13076,7 +13076,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -13208,7 +13208,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13406,7 +13406,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13505,7 +13505,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>

--- a/docs/d/73/inyear.xlsx
+++ b/docs/d/73/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 28 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="P3" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" s="9" t="n">
         <v>0</v>
@@ -996,7 +996,7 @@
         <v>0</v>
       </c>
       <c r="S3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" s="9" t="n">
         <v>0</v>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1312,8 +1312,8 @@
       <c r="T6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U6" s="9" t="n">
-        <v>0</v>
+      <c r="U6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V6" s="9" t="n">
         <v>0</v>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" s="10" t="n">
         <v>1</v>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1743,8 +1743,8 @@
       <c r="Y10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="9" t="n">
-        <v>0</v>
+      <c r="Z10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA10" s="10" t="n">
         <v>1</v>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1949,8 +1949,8 @@
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="10" t="n">
         <v>1</v>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2151,8 +2151,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3185,8 +3185,8 @@
       <c r="Y24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z24" s="9" t="n">
-        <v>0</v>
+      <c r="Z24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA24" s="10" t="n">
         <v>1</v>
@@ -3422,7 +3422,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3492,8 +3492,8 @@
       <c r="Y27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="9" t="n">
-        <v>0</v>
+      <c r="Z27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" s="10" t="n">
         <v>1</v>
@@ -4040,7 +4040,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4095,8 +4095,8 @@
       <c r="T33" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U33" s="9" t="n">
-        <v>0</v>
+      <c r="U33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V33" s="10" t="n">
         <v>4</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4417,8 +4417,8 @@
       <c r="Y36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z36" s="9" t="n">
-        <v>0</v>
+      <c r="Z36" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA36" s="10" t="n">
         <v>1</v>
@@ -4549,7 +4549,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4563,13 +4563,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4610,8 +4610,8 @@
       <c r="V38" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W38" s="9" t="n">
-        <v>3</v>
+      <c r="W38" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X38" s="10" t="n">
         <v>7</v>
@@ -4792,7 +4792,7 @@
         </is>
       </c>
       <c r="P40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40" s="9" t="n">
         <v>0</v>
@@ -4852,7 +4852,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4907,8 +4907,8 @@
       <c r="T41" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U41" s="9" t="n">
-        <v>0</v>
+      <c r="U41" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V41" s="9" t="n">
         <v>3</v>
@@ -5163,7 +5163,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5204,7 +5204,7 @@
         </is>
       </c>
       <c r="P44" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q44" s="9" t="n">
         <v>1</v>
@@ -5215,8 +5215,8 @@
       <c r="S44" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T44" s="9" t="n">
-        <v>0</v>
+      <c r="T44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U44" s="9" t="n">
         <v>0</v>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5544,8 +5544,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6447,11 +6447,11 @@
       <c r="S56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" s="9" t="n">
-        <v>0</v>
+      <c r="T56" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V56" s="9" t="n">
         <v>1</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6877,8 +6877,8 @@
       <c r="Y60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" s="9" t="n">
-        <v>0</v>
+      <c r="Z60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA60" s="10" t="n">
         <v>1</v>
@@ -7009,7 +7009,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7079,8 +7079,8 @@
       <c r="Y62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" s="9" t="n">
-        <v>0</v>
+      <c r="Z62" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA62" s="10" t="n">
         <v>1</v>
@@ -7656,7 +7656,7 @@
         </is>
       </c>
       <c r="P68" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q68" s="9" t="n">
         <v>1</v>
@@ -8077,7 +8077,7 @@
         <v>0</v>
       </c>
       <c r="S72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" s="9" t="n">
         <v>0</v>
@@ -9372,7 +9372,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9386,17 +9386,17 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L85" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L85" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M85" s="7" t="n">
@@ -9430,11 +9430,11 @@
       <c r="U85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V85" s="9" t="n">
-        <v>3</v>
+      <c r="V85" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X85" s="10" t="n">
         <v>4</v>
@@ -9442,8 +9442,8 @@
       <c r="Y85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z85" s="9" t="n">
-        <v>0</v>
+      <c r="Z85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA85" s="10" t="n">
         <v>1</v>
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9753,8 +9753,8 @@
       <c r="Y88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="9" t="n">
-        <v>0</v>
+      <c r="Z88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA88" s="10" t="n">
         <v>1</v>
@@ -9990,7 +9990,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -10060,8 +10060,8 @@
       <c r="Y91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" s="9" t="n">
-        <v>0</v>
+      <c r="Z91" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA91" s="10" t="n">
         <v>1</v>
@@ -10507,7 +10507,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10577,8 +10577,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10858,7 +10858,7 @@
         <v>2</v>
       </c>
       <c r="Q99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R99" s="9" t="n">
         <v>0</v>
@@ -11683,7 +11683,7 @@
         </is>
       </c>
       <c r="P107" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q107" s="9" t="n">
         <v>0</v>
@@ -12099,7 +12099,7 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q111" s="9" t="n">
         <v>0</v>
@@ -12470,7 +12470,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12540,8 +12540,8 @@
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
@@ -12615,7 +12615,7 @@
         <v>0</v>
       </c>
       <c r="Q116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R116" s="9" t="n">
         <v>0</v>
@@ -12845,7 +12845,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -12878,7 +12878,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -12911,7 +12911,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -13010,7 +13010,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -13076,7 +13076,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -13109,7 +13109,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -13142,7 +13142,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -13175,7 +13175,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -13241,7 +13241,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13274,7 +13274,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13439,7 +13439,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13454,7 +13454,7 @@
         <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -13472,7 +13472,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -13505,7 +13505,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13538,7 +13538,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13670,7 +13670,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>

--- a/docs/d/73/inyear.xlsx
+++ b/docs/d/73/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>5</v>
+        <v>-7</v>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
@@ -960,17 +960,17 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M3" s="7" t="n">
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="P4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="9" t="n">
         <v>0</v>
@@ -1105,8 +1105,8 @@
       <c r="U4" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="9" t="n">
-        <v>3</v>
+      <c r="V4" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1166,17 +1166,17 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M5" s="7" t="n">
@@ -1271,17 +1271,17 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M6" s="7" t="n">
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="9" t="n">
         <v>1</v>
@@ -1316,7 +1316,7 @@
         <v>1</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1376,13 +1376,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
@@ -1477,17 +1477,17 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M8" s="7" t="n">
@@ -1582,17 +1582,17 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M9" s="7" t="n">
@@ -1732,7 +1732,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1788,13 +1788,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
@@ -1893,13 +1893,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2139,11 +2139,11 @@
       <c r="U14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="9" t="n">
-        <v>1</v>
+      <c r="V14" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>5</v>
@@ -2196,13 +2196,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" s="9" t="n">
         <v>0</v>
@@ -2301,13 +2301,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2507,13 +2507,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
@@ -2545,8 +2545,8 @@
       <c r="S18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T18" s="9" t="n">
-        <v>0</v>
+      <c r="T18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U18" s="9" t="n">
         <v>0</v>
@@ -2612,13 +2612,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2717,13 +2717,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2923,13 +2923,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
@@ -3028,13 +3028,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
@@ -3230,13 +3230,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
@@ -3331,17 +3331,17 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M26" s="7" t="n">
@@ -3436,17 +3436,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M27" s="7" t="n">
@@ -3481,7 +3481,7 @@
         <v>1</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3541,13 +3541,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
@@ -3642,13 +3642,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3949,13 +3949,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
@@ -4054,13 +4054,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>4</v>
       </c>
       <c r="W33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X33" s="9" t="n">
         <v>3</v>
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>0</v>
@@ -4260,13 +4260,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
@@ -4361,13 +4361,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
@@ -4563,13 +4563,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>4</v>
       </c>
       <c r="W38" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X38" s="10" t="n">
         <v>7</v>
@@ -4664,13 +4664,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4765,13 +4765,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L40" s="8" t="inlineStr">
         <is>
@@ -4809,8 +4809,8 @@
       <c r="U40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V40" s="9" t="n">
-        <v>3</v>
+      <c r="V40" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -4866,13 +4866,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L41" s="8" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4971,13 +4971,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -5015,11 +5015,11 @@
       <c r="U42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V42" s="9" t="n">
-        <v>3</v>
+      <c r="V42" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" s="9" t="n">
         <v>3</v>
@@ -5076,13 +5076,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L43" s="8" t="inlineStr">
         <is>
@@ -5177,17 +5177,17 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L44" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M44" s="7" t="n">
@@ -5225,7 +5225,7 @@
         <v>4</v>
       </c>
       <c r="W44" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X44" s="10" t="n">
         <v>6</v>
@@ -5282,13 +5282,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
@@ -5383,17 +5383,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M46" s="7" t="n">
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5488,13 +5488,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="P47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q47" s="9" t="n">
         <v>1</v>
@@ -5532,8 +5532,8 @@
       <c r="U47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V47" s="9" t="n">
-        <v>3</v>
+      <c r="V47" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5589,17 +5589,17 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L48" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M48" s="7" t="n">
@@ -5633,8 +5633,8 @@
       <c r="U48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="9" t="n">
-        <v>3</v>
+      <c r="V48" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5694,13 +5694,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L49" s="8" t="inlineStr">
         <is>
@@ -5795,13 +5795,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L50" s="8" t="inlineStr">
         <is>
@@ -5896,13 +5896,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -6001,13 +6001,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
@@ -6045,11 +6045,11 @@
       <c r="U52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V52" s="9" t="n">
-        <v>0</v>
+      <c r="V52" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X52" s="10" t="n">
         <v>5</v>
@@ -6106,13 +6106,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6207,13 +6207,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
@@ -6245,11 +6245,11 @@
       <c r="S54" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" s="9" t="n">
-        <v>0</v>
+      <c r="T54" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V54" s="9" t="n">
         <v>1</v>
@@ -6308,13 +6308,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -6409,13 +6409,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6615,13 +6615,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
@@ -6662,8 +6662,8 @@
       <c r="V58" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W58" s="9" t="n">
-        <v>3</v>
+      <c r="W58" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X58" s="9" t="n">
         <v>3</v>
@@ -6720,13 +6720,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L59" s="8" t="inlineStr">
         <is>
@@ -6821,17 +6821,17 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L60" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M60" s="7" t="n">
@@ -6869,7 +6869,7 @@
         <v>4</v>
       </c>
       <c r="W60" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X60" s="10" t="n">
         <v>5</v>
@@ -6922,17 +6922,17 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L61" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M61" s="7" t="n">
@@ -7023,13 +7023,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L62" s="8" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L63" s="8" t="inlineStr">
         <is>
@@ -7225,13 +7225,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L64" s="8" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -7326,13 +7326,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="8" t="inlineStr">
         <is>
@@ -7427,13 +7427,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L66" s="8" t="inlineStr">
         <is>
@@ -7528,13 +7528,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L67" s="8" t="inlineStr">
         <is>
@@ -7629,13 +7629,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
@@ -7734,17 +7734,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L69" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M69" s="7" t="n">
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7940,13 +7940,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -7984,11 +7984,11 @@
       <c r="U71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V71" s="9" t="n">
-        <v>0</v>
+      <c r="V71" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X71" s="9" t="n">
         <v>0</v>
@@ -8041,13 +8041,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
@@ -8146,13 +8146,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>2</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -8251,13 +8251,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L74" s="8" t="inlineStr">
         <is>
@@ -8352,13 +8352,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L75" s="8" t="inlineStr">
         <is>
@@ -8453,13 +8453,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8558,13 +8558,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8663,17 +8663,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L78" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M78" s="7" t="n">
@@ -8707,8 +8707,8 @@
       <c r="U78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V78" s="9" t="n">
-        <v>1</v>
+      <c r="V78" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8764,13 +8764,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>0</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -8869,13 +8869,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8970,13 +8970,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L81" s="8" t="inlineStr">
         <is>
@@ -9008,8 +9008,8 @@
       <c r="S81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T81" s="9" t="n">
-        <v>0</v>
+      <c r="T81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U81" s="9" t="n">
         <v>0</v>
@@ -9071,13 +9071,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -9176,13 +9176,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9281,17 +9281,17 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L84" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M84" s="7" t="n">
@@ -9310,8 +9310,8 @@
       <c r="P84" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q84" s="9" t="n">
-        <v>1</v>
+      <c r="Q84" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R84" s="9" t="n">
         <v>0</v>
@@ -9326,7 +9326,7 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9386,17 +9386,17 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L85" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M85" s="7" t="n">
@@ -9434,7 +9434,7 @@
         <v>4</v>
       </c>
       <c r="W85" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X85" s="10" t="n">
         <v>4</v>
@@ -9477,7 +9477,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9491,13 +9491,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L86" s="8" t="inlineStr">
         <is>
@@ -9535,8 +9535,8 @@
       <c r="U86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V86" s="9" t="n">
-        <v>3</v>
+      <c r="V86" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
@@ -9592,17 +9592,17 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L87" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L87" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M87" s="7" t="n">
@@ -9697,13 +9697,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L88" s="8" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>0</v>
       </c>
       <c r="Q89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89" s="9" t="n">
         <v>0</v>
@@ -9846,7 +9846,7 @@
         <v>4</v>
       </c>
       <c r="W89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X89" s="10" t="n">
         <v>5</v>
@@ -9899,13 +9899,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L90" s="8" t="inlineStr">
         <is>
@@ -10004,13 +10004,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L91" s="8" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
@@ -10105,13 +10105,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
@@ -10210,17 +10210,17 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-21</v>
+      </c>
+      <c r="L93" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M93" s="7" t="n">
@@ -10311,13 +10311,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -10416,13 +10416,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L95" s="8" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -10521,17 +10521,17 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L96" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M96" s="7" t="n">
@@ -10548,16 +10548,16 @@
         </is>
       </c>
       <c r="P96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T96" s="9" t="n">
         <v>0</v>
@@ -10622,13 +10622,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L97" s="8" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
@@ -10723,13 +10723,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10828,13 +10828,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10933,13 +10933,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="L100" s="8" t="inlineStr">
         <is>
@@ -11034,13 +11034,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -11139,17 +11139,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L102" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M102" s="7" t="n">
@@ -11240,13 +11240,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>0</v>
       </c>
       <c r="V103" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
@@ -11345,13 +11345,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L104" s="8" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -11450,13 +11450,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L105" s="8" t="inlineStr">
         <is>
@@ -11551,13 +11551,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L106" s="8" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11656,13 +11656,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L107" s="8" t="inlineStr">
         <is>
@@ -11700,8 +11700,8 @@
       <c r="U107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V107" s="9" t="n">
-        <v>3</v>
+      <c r="V107" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -11761,13 +11761,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -11866,17 +11866,17 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L109" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M109" s="7" t="n">
@@ -12019,7 +12019,7 @@
         <v>4</v>
       </c>
       <c r="W110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X110" s="10" t="n">
         <v>4</v>
@@ -12072,13 +12072,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -12177,13 +12177,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L112" s="8" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>2</v>
       </c>
       <c r="R112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S112" s="9" t="n">
         <v>0</v>
@@ -12379,13 +12379,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
@@ -12484,13 +12484,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L115" s="8" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -12585,13 +12585,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L116" s="8" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
@@ -12686,17 +12686,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L117" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M117" s="7" t="n">
@@ -12845,7 +12845,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -12860,7 +12860,7 @@
         <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -12893,7 +12893,7 @@
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -12911,7 +12911,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -12944,7 +12944,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -13025,7 +13025,7 @@
         <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -13142,7 +13142,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -13157,7 +13157,7 @@
         <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -13175,7 +13175,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -13190,7 +13190,7 @@
         <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -13208,7 +13208,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13241,7 +13241,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13289,7 +13289,7 @@
         <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -13340,7 +13340,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13355,7 +13355,7 @@
         <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -13373,7 +13373,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13388,7 +13388,7 @@
         <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -13406,7 +13406,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13439,7 +13439,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13454,7 +13454,7 @@
         <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -13487,7 +13487,7 @@
         <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -13520,7 +13520,7 @@
         <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -13553,7 +13553,7 @@
         <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -13586,7 +13586,7 @@
         <v>5</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -13604,7 +13604,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -13652,7 +13652,7 @@
         <v>5</v>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -13685,7 +13685,7 @@
         <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/73/inyear.xlsx
+++ b/docs/d/73/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/73/inyear.xlsx
+++ b/docs/d/73/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/73/inyear.xlsx
+++ b/docs/d/73/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/73/inyear.xlsx
+++ b/docs/d/73/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/73/inyear.xlsx
+++ b/docs/d/73/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="P4" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="9" t="n">
         <v>0</v>
@@ -1788,13 +1788,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -2247,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="X15" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y15" s="9" t="n">
         <v>0</v>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -2446,8 +2446,8 @@
       <c r="U17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="9" t="n">
-        <v>3</v>
+      <c r="V17" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -3949,13 +3949,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
@@ -4361,13 +4361,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         </is>
       </c>
       <c r="P40" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q40" s="9" t="n">
         <v>0</v>
@@ -4852,7 +4852,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4866,13 +4866,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L41" s="8" t="inlineStr">
         <is>
@@ -4910,8 +4910,8 @@
       <c r="U41" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V41" s="9" t="n">
-        <v>3</v>
+      <c r="V41" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -4971,13 +4971,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>4</v>
       </c>
       <c r="W42" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X42" s="9" t="n">
         <v>3</v>
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L44" s="8" t="inlineStr">
         <is>
@@ -5282,13 +5282,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="P45" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q45" s="9" t="n">
         <v>0</v>
@@ -5327,7 +5327,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5383,13 +5383,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
@@ -5488,13 +5488,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>4</v>
       </c>
       <c r="W47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X47" s="9" t="n">
         <v>1</v>
@@ -5932,7 +5932,7 @@
         <v>1</v>
       </c>
       <c r="S51" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T51" s="9" t="n">
         <v>0</v>
@@ -6106,13 +6106,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6242,8 +6242,8 @@
       <c r="R54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S54" s="9" t="n">
-        <v>1</v>
+      <c r="S54" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T54" s="10" t="n">
         <v>1</v>
@@ -6821,13 +6821,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L60" s="8" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>4</v>
       </c>
       <c r="W60" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X60" s="10" t="n">
         <v>5</v>
@@ -6922,13 +6922,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="L61" s="8" t="inlineStr">
         <is>
@@ -7427,13 +7427,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L66" s="8" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         </is>
       </c>
       <c r="P72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q72" s="9" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>0</v>
       </c>
       <c r="S76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T76" s="9" t="n">
         <v>0</v>
@@ -8869,13 +8869,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -9176,13 +9176,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L85" s="8" t="inlineStr">
         <is>
@@ -9697,13 +9697,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L88" s="8" t="inlineStr">
         <is>
@@ -10311,13 +10311,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10521,13 +10521,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="L96" s="8" t="inlineStr">
         <is>
@@ -10550,8 +10550,8 @@
       <c r="P96" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q96" s="9" t="n">
-        <v>1</v>
+      <c r="Q96" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R96" s="9" t="n">
         <v>0</v>
@@ -10622,13 +10622,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="L97" s="8" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
@@ -11656,17 +11656,17 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L107" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L107" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M107" s="7" t="n">
@@ -11704,7 +11704,7 @@
         <v>4</v>
       </c>
       <c r="W107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X107" s="10" t="n">
         <v>4</v>
@@ -12365,7 +12365,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12379,13 +12379,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
@@ -12414,11 +12414,11 @@
       <c r="R114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S114" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T114" s="9" t="n">
-        <v>0</v>
+      <c r="S114" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U114" s="9" t="n">
         <v>0</v>
@@ -12427,7 +12427,7 @@
         <v>4</v>
       </c>
       <c r="W114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X114" s="10" t="n">
         <v>7</v>
@@ -12944,7 +12944,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -13142,7 +13142,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -13241,7 +13241,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13538,7 +13538,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13619,7 +13619,7 @@
         <v>5</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -13670,7 +13670,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>

--- a/docs/d/73/inyear.xlsx
+++ b/docs/d/73/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -896,8 +896,8 @@
       <c r="T2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U2" s="9" t="n">
-        <v>0</v>
+      <c r="U2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V2" s="10" t="n">
         <v>4</v>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>4</v>
       </c>
       <c r="W4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" s="10" t="n">
         <v>7</v>
@@ -1166,17 +1166,17 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L5" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M5" s="7" t="n">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1306,8 +1306,8 @@
       <c r="R6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S6" s="9" t="n">
-        <v>1</v>
+      <c r="S6" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T6" s="10" t="n">
         <v>1</v>
@@ -1477,13 +1477,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2196,13 +2196,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2240,8 +2240,8 @@
       <c r="U15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="9" t="n">
-        <v>1</v>
+      <c r="V15" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2301,13 +2301,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
@@ -2507,13 +2507,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
@@ -2612,13 +2612,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>4</v>
       </c>
       <c r="W19" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X19" s="10" t="n">
         <v>5</v>
@@ -2717,13 +2717,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2923,13 +2923,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="P24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="9" t="n">
         <v>0</v>
@@ -3167,8 +3167,8 @@
       <c r="S24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T24" s="9" t="n">
-        <v>0</v>
+      <c r="T24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U24" s="9" t="n">
         <v>0</v>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="X24" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y24" s="9" t="n">
         <v>0</v>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3331,13 +3331,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
@@ -3375,14 +3375,14 @@
       <c r="U26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V26" s="9" t="n">
-        <v>3</v>
+      <c r="V26" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X26" s="9" t="n">
-        <v>3</v>
+      <c r="X26" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y26" s="9" t="n">
         <v>0</v>
@@ -3848,17 +3848,17 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M31" s="7" t="n">
@@ -3893,7 +3893,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3999,8 +3999,8 @@
       <c r="W32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X32" s="9" t="n">
-        <v>1</v>
+      <c r="X32" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y32" s="9" t="n">
         <v>0</v>
@@ -4104,8 +4104,8 @@
       <c r="W33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="X33" s="9" t="n">
-        <v>3</v>
+      <c r="X33" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y33" s="9" t="n">
         <v>0</v>
@@ -4209,8 +4209,8 @@
       <c r="W34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X34" s="9" t="n">
-        <v>3</v>
+      <c r="X34" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y34" s="9" t="n">
         <v>0</v>
@@ -4563,13 +4563,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>4</v>
       </c>
       <c r="W38" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X38" s="10" t="n">
         <v>7</v>
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5421,8 +5421,8 @@
       <c r="S46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T46" s="9" t="n">
-        <v>0</v>
+      <c r="T46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U46" s="9" t="n">
         <v>0</v>
@@ -5488,13 +5488,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="P47" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q47" s="9" t="n">
         <v>1</v>
@@ -5536,7 +5536,7 @@
         <v>4</v>
       </c>
       <c r="W47" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X47" s="9" t="n">
         <v>1</v>
@@ -5589,13 +5589,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L48" s="8" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>4</v>
       </c>
       <c r="W48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X48" s="10" t="n">
         <v>5</v>
@@ -6106,13 +6106,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -6344,7 +6344,7 @@
         <v>0</v>
       </c>
       <c r="S55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T55" s="9" t="n">
         <v>0</v>
@@ -6409,13 +6409,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6720,13 +6720,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-15</v>
+        <v>1</v>
       </c>
       <c r="L59" s="8" t="inlineStr">
         <is>
@@ -6764,11 +6764,11 @@
       <c r="U59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V59" s="9" t="n">
-        <v>0</v>
+      <c r="V59" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X59" s="9" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6821,17 +6821,17 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L60" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M60" s="7" t="n">
@@ -6868,8 +6868,8 @@
       <c r="V60" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W60" s="9" t="n">
-        <v>3</v>
+      <c r="W60" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X60" s="10" t="n">
         <v>5</v>
@@ -6922,13 +6922,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L61" s="8" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7266,8 +7266,8 @@
       <c r="T64" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U64" s="9" t="n">
-        <v>0</v>
+      <c r="U64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V64" s="9" t="n">
         <v>2</v>
@@ -8352,13 +8352,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L75" s="8" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>4</v>
       </c>
       <c r="W77" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X77" s="10" t="n">
         <v>6</v>
@@ -9491,13 +9491,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L86" s="8" t="inlineStr">
         <is>
@@ -10105,13 +10105,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
@@ -11139,13 +11139,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L102" s="8" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>0</v>
       </c>
       <c r="S102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T102" s="10" t="n">
         <v>1</v>
@@ -11642,7 +11642,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11694,8 +11694,8 @@
       <c r="S107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T107" s="9" t="n">
-        <v>0</v>
+      <c r="T107" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U107" s="9" t="n">
         <v>0</v>
@@ -11788,7 +11788,7 @@
         </is>
       </c>
       <c r="P108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q108" s="9" t="n">
         <v>0</v>
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11866,13 +11866,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="L109" s="8" t="inlineStr">
         <is>
@@ -11904,14 +11904,14 @@
       <c r="S109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T109" s="9" t="n">
-        <v>0</v>
+      <c r="T109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -12058,7 +12058,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12110,8 +12110,8 @@
       <c r="S111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T111" s="9" t="n">
-        <v>0</v>
+      <c r="T111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U111" s="9" t="n">
         <v>0</v>
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L117" s="8" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -12860,7 +12860,7 @@
         <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -12944,7 +12944,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -13010,7 +13010,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -13058,7 +13058,7 @@
         <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -13175,7 +13175,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -13274,7 +13274,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13289,7 +13289,7 @@
         <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -13307,7 +13307,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13604,7 +13604,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -13637,7 +13637,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
